--- a/synoptic/data/PR wetland sampling data.xlsx
+++ b/synoptic/data/PR wetland sampling data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\PR-wetlands\synoptic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD58FF6-3BC0-4779-9D47-892F0A45995D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21D29EB-3F89-4725-9679-8A4A7C7433EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PR wetland sampling data" sheetId="1" r:id="rId1"/>
@@ -1341,1011 +1341,1002 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B2" s="1">
-        <v>44363</v>
+        <v>44124</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="E2" s="3">
+        <v>150</v>
+      </c>
+      <c r="F2" s="3">
+        <v>38</v>
+      </c>
+      <c r="G2" s="3">
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
+        <v>52</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.47916666666666669</v>
+        <v>53</v>
       </c>
       <c r="L2">
-        <v>-1.49</v>
+        <v>13.19</v>
       </c>
       <c r="M2">
-        <v>559</v>
-      </c>
-      <c r="Q2">
-        <v>30.05</v>
-      </c>
-      <c r="R2">
-        <v>86</v>
-      </c>
-      <c r="S2">
-        <v>72</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1">
-        <v>44363</v>
+        <v>44124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="E3" s="3">
+        <v>150</v>
+      </c>
+      <c r="F3" s="3">
+        <v>38</v>
+      </c>
+      <c r="G3" s="3">
+        <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="s">
-        <v>73</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0.47222222222222227</v>
+        <v>53</v>
       </c>
       <c r="L3">
-        <v>12.31</v>
+        <v>11.71</v>
       </c>
       <c r="M3">
-        <v>6348</v>
-      </c>
-      <c r="Q3">
-        <v>30.05</v>
-      </c>
-      <c r="R3">
-        <v>86</v>
-      </c>
-      <c r="S3">
-        <v>72</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B4" s="1">
-        <v>44363</v>
+        <v>44124</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="E4" s="3">
+        <v>150</v>
+      </c>
+      <c r="F4" s="3">
+        <v>38</v>
+      </c>
+      <c r="G4" s="3">
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>73</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0.47222222222222227</v>
+        <v>53</v>
       </c>
       <c r="L4">
-        <v>11.59</v>
+        <v>6.82</v>
       </c>
       <c r="M4">
-        <v>6617</v>
-      </c>
-      <c r="Q4">
-        <v>30.05</v>
-      </c>
-      <c r="R4">
-        <v>86</v>
-      </c>
-      <c r="S4">
-        <v>72</v>
+        <v>840</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1">
-        <v>44363</v>
+        <v>44124</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="E5" s="3">
+        <v>150</v>
+      </c>
+      <c r="F5" s="3">
+        <v>38</v>
+      </c>
+      <c r="G5" s="3">
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
         <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.47916666666666669</v>
+        <v>53</v>
       </c>
       <c r="L5">
-        <v>-1.89</v>
+        <v>18.23</v>
       </c>
       <c r="M5">
-        <v>491</v>
-      </c>
-      <c r="Q5">
-        <v>30.05</v>
-      </c>
-      <c r="R5">
-        <v>86</v>
-      </c>
-      <c r="S5">
-        <v>72</v>
+        <v>917</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B6" s="1">
-        <v>44363</v>
+        <v>44124</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="E6" s="3">
+        <v>150</v>
+      </c>
+      <c r="F6" s="3">
+        <v>38</v>
+      </c>
+      <c r="G6" s="3">
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="I6" t="s">
         <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0.47916666666666669</v>
+        <v>53</v>
       </c>
       <c r="L6">
-        <v>-1.1599999999999999</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="M6">
-        <v>780</v>
-      </c>
-      <c r="Q6">
-        <v>30.05</v>
-      </c>
-      <c r="R6">
-        <v>86</v>
-      </c>
-      <c r="S6">
-        <v>72</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>44377</v>
+        <v>44155</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="E7" s="3">
+        <v>208</v>
+      </c>
+      <c r="F7" s="3">
+        <v>44</v>
+      </c>
+      <c r="G7" s="3">
+        <v>38</v>
+      </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="K7" s="2">
-        <v>0.61805555555555558</v>
+        <v>0.4055555555555555</v>
       </c>
       <c r="L7">
-        <v>96.34</v>
+        <v>58.9</v>
       </c>
       <c r="M7">
-        <v>4942</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>44377</v>
+        <v>44155</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="E8" s="3">
+        <v>208</v>
+      </c>
+      <c r="F8" s="3">
+        <v>44</v>
+      </c>
+      <c r="G8" s="3">
+        <v>38</v>
+      </c>
       <c r="H8" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="K8" s="2">
-        <v>0.61805555555555558</v>
+        <v>0.4055555555555555</v>
       </c>
       <c r="L8">
-        <v>94.93</v>
+        <v>71.12</v>
       </c>
       <c r="M8">
-        <v>5261</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1">
-        <v>44377</v>
+        <v>44155</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="E9" s="3">
+        <v>208</v>
+      </c>
+      <c r="F9" s="3">
+        <v>44</v>
+      </c>
+      <c r="G9" s="3">
+        <v>38</v>
+      </c>
       <c r="H9" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="K9" s="2">
-        <v>0.61805555555555558</v>
+        <v>0.4055555555555555</v>
       </c>
       <c r="L9">
-        <v>91.1</v>
+        <v>53.96</v>
       </c>
       <c r="M9">
-        <v>4901</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1">
-        <v>44377</v>
+        <v>44155</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="E10" s="3">
+        <v>208</v>
+      </c>
+      <c r="F10" s="3">
+        <v>44</v>
+      </c>
+      <c r="G10" s="3">
+        <v>38</v>
+      </c>
       <c r="H10" t="s">
-        <v>107</v>
-      </c>
-      <c r="I10" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="K10" s="2">
-        <v>0.625</v>
+        <v>0.4055555555555555</v>
       </c>
       <c r="L10">
-        <v>-1.62</v>
+        <v>65.44</v>
       </c>
       <c r="M10">
-        <v>582</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1">
-        <v>44377</v>
+        <v>44155</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="E11" s="3">
+        <v>208</v>
+      </c>
+      <c r="F11" s="3">
+        <v>44</v>
+      </c>
+      <c r="G11" s="3">
+        <v>38</v>
+      </c>
       <c r="H11" t="s">
-        <v>108</v>
-      </c>
-      <c r="I11" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
       </c>
       <c r="J11" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="K11" s="2">
-        <v>0.625</v>
+        <v>0.4055555555555555</v>
       </c>
       <c r="L11">
-        <v>-2.0299999999999998</v>
+        <v>58.78</v>
       </c>
       <c r="M11">
-        <v>495</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1">
-        <v>44377</v>
+        <v>44155</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="E12" s="3">
+        <v>208</v>
+      </c>
+      <c r="F12" s="3">
+        <v>44</v>
+      </c>
+      <c r="G12" s="3">
+        <v>38</v>
+      </c>
       <c r="H12" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
         <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="K12" s="2">
-        <v>0.625</v>
+        <v>0.4055555555555555</v>
       </c>
       <c r="L12">
-        <v>-1.29</v>
+        <v>8.15</v>
       </c>
       <c r="M12">
-        <v>577</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1">
-        <v>44167</v>
+        <v>44155</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E13" s="3">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="F13" s="3">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3">
         <v>38</v>
       </c>
-      <c r="G13" s="3">
-        <v>35</v>
-      </c>
       <c r="H13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="K13" s="2">
-        <v>0.43402777777777773</v>
+        <v>0.4055555555555555</v>
       </c>
       <c r="L13">
-        <v>1532.9</v>
+        <v>6.73</v>
       </c>
       <c r="M13">
-        <v>4506</v>
+        <v>742</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1">
-        <v>44167</v>
+        <v>44155</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E14" s="3">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="F14" s="3">
+        <v>44</v>
+      </c>
+      <c r="G14" s="3">
         <v>38</v>
       </c>
-      <c r="G14" s="3">
-        <v>35</v>
-      </c>
       <c r="H14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="K14" s="2">
-        <v>0.43402777777777773</v>
+        <v>0.4055555555555555</v>
       </c>
       <c r="L14">
-        <v>2084.0100000000002</v>
+        <v>4.01</v>
       </c>
       <c r="M14">
-        <v>5925</v>
+        <v>836</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1">
-        <v>44167</v>
+        <v>44160</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E15" s="3">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="F15" s="3">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15">
-        <v>3</v>
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K15" s="2">
-        <v>0.43402777777777773</v>
+        <v>0.3979166666666667</v>
       </c>
       <c r="L15">
-        <v>2082.73</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="M15">
-        <v>5793</v>
+        <v>756</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1">
-        <v>44167</v>
+        <v>44160</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E16" s="3">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="F16" s="3">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I16" t="s">
         <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K16" s="2">
-        <v>0.4375</v>
+        <v>0.3979166666666667</v>
       </c>
       <c r="L16">
-        <v>4.42</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M16">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1">
-        <v>44167</v>
+        <v>44160</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="3">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="F17" s="3">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="I17" t="s">
         <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K17" s="2">
-        <v>0.4375</v>
+        <v>0.3979166666666667</v>
       </c>
       <c r="L17">
-        <v>6.94</v>
+        <v>3.22</v>
       </c>
       <c r="M17">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1">
+        <v>44160</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="3">
+        <v>185</v>
+      </c>
+      <c r="F18" s="3">
+        <v>44</v>
+      </c>
+      <c r="G18" s="3">
+        <v>37</v>
+      </c>
+      <c r="H18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.3979166666666667</v>
+      </c>
+      <c r="L18">
+        <v>999.53</v>
+      </c>
+      <c r="M18">
+        <v>4665</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1">
+        <v>44160</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="3">
+        <v>185</v>
+      </c>
+      <c r="F19" s="3">
+        <v>44</v>
+      </c>
+      <c r="G19" s="3">
+        <v>37</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>28</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.3979166666666667</v>
+      </c>
+      <c r="L19">
+        <v>734.6</v>
+      </c>
+      <c r="M19">
+        <v>4327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1">
+        <v>44160</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="3">
+        <v>185</v>
+      </c>
+      <c r="F20" s="3">
+        <v>44</v>
+      </c>
+      <c r="G20" s="3">
+        <v>37</v>
+      </c>
+      <c r="H20" t="s">
+        <v>33</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.3979166666666667</v>
+      </c>
+      <c r="L20">
+        <v>972.57</v>
+      </c>
+      <c r="M20">
+        <v>5621</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1">
+        <v>44160</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="3">
+        <v>185</v>
+      </c>
+      <c r="F21" s="3">
+        <v>44</v>
+      </c>
+      <c r="G21" s="3">
+        <v>37</v>
+      </c>
+      <c r="H21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0.41736111111111113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="1">
+        <v>44160</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="3">
+        <v>185</v>
+      </c>
+      <c r="F22" s="3">
+        <v>44</v>
+      </c>
+      <c r="G22" s="3">
+        <v>37</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>28</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0.41736111111111113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="1">
+        <v>44160</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" s="3">
+        <v>185</v>
+      </c>
+      <c r="F23" s="3">
+        <v>44</v>
+      </c>
+      <c r="G23" s="3">
+        <v>37</v>
+      </c>
+      <c r="H23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="J23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23" s="2">
+        <v>0.41736111111111113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="1">
+        <v>44160</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" s="3">
+        <v>185</v>
+      </c>
+      <c r="F24" s="3">
+        <v>44</v>
+      </c>
+      <c r="G24" s="3">
+        <v>37</v>
+      </c>
+      <c r="H24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>28</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="L24">
+        <v>818.74</v>
+      </c>
+      <c r="M24">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="1">
+        <v>44160</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="3">
+        <v>185</v>
+      </c>
+      <c r="F25" s="3">
+        <v>44</v>
+      </c>
+      <c r="G25" s="3">
+        <v>37</v>
+      </c>
+      <c r="H25" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="L25">
+        <v>904.21</v>
+      </c>
+      <c r="M25">
+        <v>4776</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1">
+        <v>44160</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="3">
+        <v>185</v>
+      </c>
+      <c r="F26" s="3">
+        <v>44</v>
+      </c>
+      <c r="G26" s="3">
+        <v>37</v>
+      </c>
+      <c r="H26" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26">
+        <v>3</v>
+      </c>
+      <c r="J26" t="s">
+        <v>28</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="L26">
+        <v>812.07</v>
+      </c>
+      <c r="M26">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B27" s="1">
         <v>44167</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="3">
-        <v>142</v>
-      </c>
-      <c r="F18" s="3">
-        <v>38</v>
-      </c>
-      <c r="G18" s="3">
-        <v>35</v>
-      </c>
-      <c r="H18" t="s">
-        <v>47</v>
-      </c>
-      <c r="I18" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" t="s">
-        <v>42</v>
-      </c>
-      <c r="K18" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="L18">
-        <v>7.06</v>
-      </c>
-      <c r="M18">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="1">
-        <v>44167</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="3">
-        <v>142</v>
-      </c>
-      <c r="F19" s="3">
-        <v>38</v>
-      </c>
-      <c r="G19" s="3">
-        <v>35</v>
-      </c>
-      <c r="H19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19" t="s">
-        <v>42</v>
-      </c>
-      <c r="K19" s="2">
-        <v>0.40625</v>
-      </c>
-      <c r="L19">
-        <v>1910.87</v>
-      </c>
-      <c r="M19">
-        <v>7609</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="1">
-        <v>44167</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="3">
-        <v>142</v>
-      </c>
-      <c r="F20" s="3">
-        <v>38</v>
-      </c>
-      <c r="G20" s="3">
-        <v>35</v>
-      </c>
-      <c r="H20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-      <c r="J20" t="s">
-        <v>42</v>
-      </c>
-      <c r="K20" s="2">
-        <v>0.40625</v>
-      </c>
-      <c r="L20">
-        <v>2080.4299999999998</v>
-      </c>
-      <c r="M20">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="1">
-        <v>44167</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" s="3">
-        <v>142</v>
-      </c>
-      <c r="F21" s="3">
-        <v>38</v>
-      </c>
-      <c r="G21" s="3">
-        <v>35</v>
-      </c>
-      <c r="H21" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21">
-        <v>3</v>
-      </c>
-      <c r="J21" t="s">
-        <v>42</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0.40625</v>
-      </c>
-      <c r="L21">
-        <v>2449.71</v>
-      </c>
-      <c r="M21">
-        <v>8015</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="1">
-        <v>44364</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" s="3">
-        <v>150</v>
-      </c>
-      <c r="F22" s="3">
-        <v>38</v>
-      </c>
-      <c r="H22" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22" t="s">
-        <v>88</v>
-      </c>
-      <c r="K22" s="2">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="L22">
-        <v>111.27</v>
-      </c>
-      <c r="M22">
-        <v>5590</v>
-      </c>
-      <c r="Q22">
-        <v>30.02</v>
-      </c>
-      <c r="R22">
-        <v>82</v>
-      </c>
-      <c r="S22">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="1">
-        <v>44364</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="3">
-        <v>150</v>
-      </c>
-      <c r="F23" s="3">
-        <v>38</v>
-      </c>
-      <c r="H23" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23">
-        <v>2</v>
-      </c>
-      <c r="J23" t="s">
-        <v>88</v>
-      </c>
-      <c r="K23" s="2">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="L23">
-        <v>100.81</v>
-      </c>
-      <c r="M23">
-        <v>5082</v>
-      </c>
-      <c r="Q23">
-        <v>30.02</v>
-      </c>
-      <c r="R23">
-        <v>82</v>
-      </c>
-      <c r="S23">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" s="1">
-        <v>44364</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" s="3">
-        <v>150</v>
-      </c>
-      <c r="F24" s="3">
-        <v>38</v>
-      </c>
-      <c r="H24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I24">
-        <v>3</v>
-      </c>
-      <c r="J24" t="s">
-        <v>88</v>
-      </c>
-      <c r="K24" s="2">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="L24">
-        <v>102.98</v>
-      </c>
-      <c r="M24">
-        <v>4291</v>
-      </c>
-      <c r="Q24">
-        <v>30.02</v>
-      </c>
-      <c r="R24">
-        <v>82</v>
-      </c>
-      <c r="S24">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="1">
-        <v>44364</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25" s="3">
-        <v>150</v>
-      </c>
-      <c r="F25" s="3">
-        <v>38</v>
-      </c>
-      <c r="H25" t="s">
-        <v>91</v>
-      </c>
-      <c r="I25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" t="s">
-        <v>88</v>
-      </c>
-      <c r="K25" s="2">
-        <v>0.52777777777777779</v>
-      </c>
-      <c r="L25">
-        <v>-1.65</v>
-      </c>
-      <c r="M25">
-        <v>707</v>
-      </c>
-      <c r="Q25">
-        <v>30.02</v>
-      </c>
-      <c r="R25">
-        <v>82</v>
-      </c>
-      <c r="S25">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="1">
-        <v>44364</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E26" s="3">
-        <v>150</v>
-      </c>
-      <c r="F26" s="3">
-        <v>38</v>
-      </c>
-      <c r="H26" t="s">
-        <v>92</v>
-      </c>
-      <c r="I26" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K26" s="2">
-        <v>0.52777777777777779</v>
-      </c>
-      <c r="L26">
-        <v>-1.72</v>
-      </c>
-      <c r="M26">
-        <v>662</v>
-      </c>
-      <c r="Q26">
-        <v>30.02</v>
-      </c>
-      <c r="R26">
-        <v>82</v>
-      </c>
-      <c r="S26">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="1">
-        <v>44364</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>120</v>
@@ -2354,45 +2345,39 @@
         <v>126</v>
       </c>
       <c r="E27" s="3">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F27" s="3">
         <v>38</v>
       </c>
+      <c r="G27" s="3">
+        <v>35</v>
+      </c>
       <c r="H27" t="s">
-        <v>93</v>
-      </c>
-      <c r="I27" t="s">
-        <v>23</v>
+        <v>41</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="K27" s="2">
-        <v>0.52777777777777779</v>
+        <v>0.43402777777777773</v>
       </c>
       <c r="L27">
-        <v>-1.84</v>
+        <v>1532.9</v>
       </c>
       <c r="M27">
-        <v>644</v>
-      </c>
-      <c r="Q27">
-        <v>30.02</v>
-      </c>
-      <c r="R27">
-        <v>82</v>
-      </c>
-      <c r="S27">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+        <v>4506</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1">
-        <v>44124</v>
+        <v>44167</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>120</v>
@@ -2401,36 +2386,39 @@
         <v>126</v>
       </c>
       <c r="E28" s="3">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F28" s="3">
         <v>38</v>
       </c>
       <c r="G28" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="s">
-        <v>53</v>
+        <v>42</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0.43402777777777773</v>
       </c>
       <c r="L28">
-        <v>13.19</v>
+        <v>2084.0100000000002</v>
       </c>
       <c r="M28">
-        <v>2107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+        <v>5925</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1">
-        <v>44124</v>
+        <v>44167</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>120</v>
@@ -2439,36 +2427,39 @@
         <v>126</v>
       </c>
       <c r="E29" s="3">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F29" s="3">
         <v>38</v>
       </c>
       <c r="G29" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="s">
-        <v>53</v>
+        <v>42</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0.43402777777777773</v>
       </c>
       <c r="L29">
-        <v>11.71</v>
+        <v>2082.73</v>
       </c>
       <c r="M29">
-        <v>2574</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+        <v>5793</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B30" s="1">
-        <v>44124</v>
+        <v>44167</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>120</v>
@@ -2477,36 +2468,39 @@
         <v>126</v>
       </c>
       <c r="E30" s="3">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F30" s="3">
         <v>38</v>
       </c>
       <c r="G30" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I30" t="s">
         <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>53</v>
+        <v>42</v>
+      </c>
+      <c r="K30" s="2">
+        <v>0.4375</v>
       </c>
       <c r="L30">
-        <v>6.82</v>
+        <v>4.42</v>
       </c>
       <c r="M30">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1">
-        <v>44124</v>
+        <v>44167</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>120</v>
@@ -2515,36 +2509,39 @@
         <v>126</v>
       </c>
       <c r="E31" s="3">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F31" s="3">
         <v>38</v>
       </c>
       <c r="G31" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I31" t="s">
         <v>23</v>
       </c>
       <c r="J31" t="s">
-        <v>53</v>
+        <v>42</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0.4375</v>
       </c>
       <c r="L31">
-        <v>18.23</v>
+        <v>6.94</v>
       </c>
       <c r="M31">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1">
-        <v>44124</v>
+        <v>44167</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>120</v>
@@ -2553,36 +2550,39 @@
         <v>126</v>
       </c>
       <c r="E32" s="3">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F32" s="3">
         <v>38</v>
       </c>
       <c r="G32" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I32" t="s">
         <v>23</v>
       </c>
       <c r="J32" t="s">
-        <v>53</v>
+        <v>42</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0.4375</v>
       </c>
       <c r="L32">
-        <v>4.6399999999999997</v>
+        <v>7.06</v>
       </c>
       <c r="M32">
-        <v>788</v>
+        <v>877</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>44361</v>
+        <v>44167</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>120</v>
@@ -2591,51 +2591,39 @@
         <v>126</v>
       </c>
       <c r="E33" s="3">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F33" s="3">
         <v>38</v>
       </c>
       <c r="G33" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="K33" s="2">
-        <v>0.375</v>
+        <v>0.40625</v>
       </c>
       <c r="L33">
-        <v>107.48</v>
+        <v>1910.87</v>
       </c>
       <c r="M33">
-        <v>4782</v>
-      </c>
-      <c r="Q33">
-        <v>30.11</v>
-      </c>
-      <c r="R33">
-        <v>29.7</v>
-      </c>
-      <c r="S33">
-        <v>81.5</v>
-      </c>
-      <c r="T33" t="s">
-        <v>70</v>
+        <v>7609</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1">
-        <v>44361</v>
+        <v>44167</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>120</v>
@@ -2644,51 +2632,39 @@
         <v>126</v>
       </c>
       <c r="E34" s="3">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F34" s="3">
         <v>38</v>
       </c>
       <c r="G34" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I34">
         <v>2</v>
       </c>
       <c r="J34" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="K34" s="2">
-        <v>0.375</v>
+        <v>0.40625</v>
       </c>
       <c r="L34">
-        <v>61.36</v>
+        <v>2080.4299999999998</v>
       </c>
       <c r="M34">
-        <v>4578</v>
-      </c>
-      <c r="Q34">
-        <v>30.11</v>
-      </c>
-      <c r="R34">
-        <v>29.7</v>
-      </c>
-      <c r="S34">
-        <v>81.5</v>
-      </c>
-      <c r="T34" t="s">
-        <v>70</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B35" s="1">
-        <v>44361</v>
+        <v>44167</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>120</v>
@@ -2697,585 +2673,273 @@
         <v>126</v>
       </c>
       <c r="E35" s="3">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F35" s="3">
         <v>38</v>
       </c>
       <c r="G35" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I35">
         <v>3</v>
       </c>
       <c r="J35" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="K35" s="2">
-        <v>0.375</v>
+        <v>0.40625</v>
       </c>
       <c r="L35">
-        <v>106.85</v>
+        <v>2449.71</v>
       </c>
       <c r="M35">
-        <v>5382</v>
-      </c>
-      <c r="Q35">
-        <v>30.11</v>
-      </c>
-      <c r="R35">
-        <v>29.7</v>
-      </c>
-      <c r="S35">
-        <v>81.5</v>
-      </c>
-      <c r="T35" t="s">
-        <v>70</v>
+        <v>8015</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="B36" s="1">
-        <v>44361</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="3">
-        <v>150</v>
-      </c>
-      <c r="F36" s="3">
-        <v>38</v>
-      </c>
-      <c r="G36" s="3">
-        <v>38</v>
-      </c>
+        <v>44180</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
       <c r="H36" t="s">
-        <v>55</v>
-      </c>
-      <c r="I36" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" t="s">
-        <v>69</v>
-      </c>
-      <c r="K36" s="2">
-        <v>0.38194444444444442</v>
+        <v>58</v>
       </c>
       <c r="L36">
-        <v>-0.89</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="M36">
-        <v>592</v>
-      </c>
-      <c r="Q36">
-        <v>30.11</v>
-      </c>
-      <c r="R36">
-        <v>29.7</v>
-      </c>
-      <c r="S36">
-        <v>81.5</v>
-      </c>
-      <c r="T36" t="s">
-        <v>70</v>
+        <v>899</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="B37" s="1">
-        <v>44361</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" s="3">
-        <v>150</v>
-      </c>
-      <c r="F37" s="3">
-        <v>38</v>
-      </c>
-      <c r="G37" s="3">
-        <v>38</v>
-      </c>
+        <v>44180</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
       <c r="H37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I37" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" t="s">
-        <v>69</v>
-      </c>
-      <c r="K37" s="2">
-        <v>0.38194444444444442</v>
+        <v>59</v>
       </c>
       <c r="L37">
-        <v>-1.81</v>
+        <v>3.22</v>
       </c>
       <c r="M37">
-        <v>587</v>
-      </c>
-      <c r="Q37">
-        <v>30.11</v>
-      </c>
-      <c r="R37">
-        <v>29.7</v>
-      </c>
-      <c r="S37">
-        <v>81.5</v>
-      </c>
-      <c r="T37" t="s">
-        <v>70</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="B38" s="1">
-        <v>44361</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" s="3">
-        <v>150</v>
-      </c>
-      <c r="F38" s="3">
-        <v>38</v>
-      </c>
-      <c r="G38" s="3">
-        <v>38</v>
-      </c>
+        <v>44180</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
       <c r="H38" t="s">
-        <v>57</v>
-      </c>
-      <c r="I38" t="s">
-        <v>23</v>
-      </c>
-      <c r="J38" t="s">
-        <v>69</v>
-      </c>
-      <c r="K38" s="2">
-        <v>0.38194444444444442</v>
+        <v>60</v>
       </c>
       <c r="L38">
-        <v>-0.53</v>
+        <v>2.52</v>
       </c>
       <c r="M38">
-        <v>574</v>
-      </c>
-      <c r="Q38">
-        <v>30.11</v>
-      </c>
-      <c r="R38">
-        <v>29.7</v>
-      </c>
-      <c r="S38">
-        <v>81.5</v>
-      </c>
-      <c r="T38" t="s">
-        <v>70</v>
+        <v>779</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B39" s="1">
-        <v>44155</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="3">
-        <v>208</v>
-      </c>
-      <c r="F39" s="3">
-        <v>44</v>
-      </c>
-      <c r="G39" s="3">
-        <v>38</v>
-      </c>
+        <v>44180</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
       <c r="H39" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="J39" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="2">
-        <v>0.4055555555555555</v>
+        <v>61</v>
       </c>
       <c r="L39">
-        <v>58.9</v>
+        <v>3.04</v>
       </c>
       <c r="M39">
-        <v>1809</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B40" s="1">
-        <v>44155</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" s="3">
-        <v>208</v>
-      </c>
-      <c r="F40" s="3">
-        <v>44</v>
-      </c>
-      <c r="G40" s="3">
-        <v>38</v>
-      </c>
+        <v>44180</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
       <c r="H40" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40">
-        <v>2</v>
-      </c>
-      <c r="J40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="2">
-        <v>0.4055555555555555</v>
+        <v>62</v>
       </c>
       <c r="L40">
-        <v>71.12</v>
+        <v>2.44</v>
       </c>
       <c r="M40">
-        <v>2180</v>
+        <v>923</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B41" s="1">
-        <v>44155</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E41" s="3">
-        <v>208</v>
-      </c>
-      <c r="F41" s="3">
-        <v>44</v>
-      </c>
-      <c r="G41" s="3">
-        <v>38</v>
-      </c>
+        <v>44180</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
       <c r="H41" t="s">
-        <v>19</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="2">
-        <v>0.4055555555555555</v>
+        <v>63</v>
       </c>
       <c r="L41">
-        <v>53.96</v>
+        <v>2.39</v>
       </c>
       <c r="M41">
-        <v>2378</v>
+        <v>719</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B42" s="1">
-        <v>44155</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E42" s="3">
-        <v>208</v>
-      </c>
-      <c r="F42" s="3">
-        <v>44</v>
-      </c>
-      <c r="G42" s="3">
-        <v>38</v>
-      </c>
+        <v>44180</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
       <c r="H42" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42">
-        <v>2</v>
-      </c>
-      <c r="J42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" s="2">
-        <v>0.4055555555555555</v>
+        <v>64</v>
       </c>
       <c r="L42">
-        <v>65.44</v>
+        <v>2.97</v>
       </c>
       <c r="M42">
-        <v>2350</v>
+        <v>893</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B43" s="1">
-        <v>44155</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43" s="3">
-        <v>208</v>
-      </c>
-      <c r="F43" s="3">
-        <v>44</v>
-      </c>
-      <c r="G43" s="3">
-        <v>38</v>
-      </c>
+        <v>44349</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
       <c r="H43" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43">
-        <v>3</v>
-      </c>
-      <c r="J43" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="2">
-        <v>0.4055555555555555</v>
+        <v>58</v>
       </c>
       <c r="L43">
-        <v>58.78</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="M43">
-        <v>2279</v>
+        <v>882</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B44" s="1">
-        <v>44155</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44" s="3">
-        <v>208</v>
-      </c>
-      <c r="F44" s="3">
-        <v>44</v>
-      </c>
-      <c r="G44" s="3">
-        <v>38</v>
-      </c>
+        <v>44349</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
       <c r="H44" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="2">
-        <v>0.4055555555555555</v>
+        <v>59</v>
       </c>
       <c r="L44">
-        <v>8.15</v>
+        <v>-2.38</v>
       </c>
       <c r="M44">
-        <v>682</v>
+        <v>484</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B45" s="1">
-        <v>44155</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E45" s="3">
-        <v>208</v>
-      </c>
-      <c r="F45" s="3">
-        <v>44</v>
-      </c>
-      <c r="G45" s="3">
-        <v>38</v>
-      </c>
+        <v>44349</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
       <c r="H45" t="s">
-        <v>24</v>
-      </c>
-      <c r="I45" t="s">
-        <v>23</v>
-      </c>
-      <c r="J45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" s="2">
-        <v>0.4055555555555555</v>
+        <v>60</v>
       </c>
       <c r="L45">
-        <v>6.73</v>
+        <v>-1.98</v>
       </c>
       <c r="M45">
-        <v>742</v>
+        <v>525</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B46" s="1">
-        <v>44155</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" s="3">
-        <v>208</v>
-      </c>
-      <c r="F46" s="3">
-        <v>44</v>
-      </c>
-      <c r="G46" s="3">
-        <v>38</v>
-      </c>
+        <v>44349</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
       <c r="H46" t="s">
-        <v>25</v>
-      </c>
-      <c r="I46" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K46" s="2">
-        <v>0.4055555555555555</v>
+        <v>62</v>
       </c>
       <c r="L46">
-        <v>4.01</v>
+        <v>-1.3</v>
       </c>
       <c r="M46">
-        <v>836</v>
+        <v>593</v>
+      </c>
+      <c r="T46" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B47" s="1">
-        <v>44375</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" s="3">
-        <v>208</v>
-      </c>
-      <c r="F47" s="3">
-        <v>44</v>
-      </c>
+        <v>44349</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
       <c r="H47" t="s">
-        <v>94</v>
-      </c>
-      <c r="I47" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" t="s">
-        <v>95</v>
-      </c>
-      <c r="K47" s="2">
-        <v>0.41666666666666669</v>
+        <v>63</v>
       </c>
       <c r="L47">
-        <v>-2.06</v>
+        <v>-1.9</v>
       </c>
       <c r="M47">
-        <v>701</v>
-      </c>
-      <c r="Q47">
-        <v>30.08</v>
-      </c>
-      <c r="R47">
-        <v>82</v>
+        <v>671</v>
       </c>
       <c r="T47" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B48" s="1">
-        <v>44375</v>
+        <v>44358</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>120</v>
@@ -3284,45 +2948,48 @@
         <v>125</v>
       </c>
       <c r="E48" s="3">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F48" s="3">
         <v>44</v>
       </c>
+      <c r="G48" s="3">
+        <v>37</v>
+      </c>
       <c r="H48" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="I48" t="s">
         <v>23</v>
       </c>
       <c r="J48" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K48" s="2">
-        <v>0.41666666666666669</v>
+        <v>0.61111111111111105</v>
       </c>
       <c r="L48">
-        <v>-2.04</v>
+        <v>0.09</v>
       </c>
       <c r="M48">
-        <v>657</v>
+        <v>680</v>
       </c>
       <c r="Q48">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="R48">
         <v>82</v>
       </c>
       <c r="T48" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B49" s="1">
-        <v>44375</v>
+        <v>44358</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>120</v>
@@ -3331,45 +2998,48 @@
         <v>125</v>
       </c>
       <c r="E49" s="3">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F49" s="3">
         <v>44</v>
       </c>
+      <c r="G49" s="3">
+        <v>37</v>
+      </c>
       <c r="H49" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="I49" t="s">
         <v>23</v>
       </c>
       <c r="J49" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K49" s="2">
-        <v>0.41666666666666669</v>
+        <v>0.61111111111111105</v>
       </c>
       <c r="L49">
-        <v>-1.59</v>
+        <v>2.14</v>
       </c>
       <c r="M49">
-        <v>556</v>
+        <v>862</v>
       </c>
       <c r="Q49">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="R49">
         <v>82</v>
       </c>
       <c r="T49" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B50" s="1">
-        <v>44375</v>
+        <v>44358</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>120</v>
@@ -3378,42 +3048,48 @@
         <v>125</v>
       </c>
       <c r="E50" s="3">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F50" s="3">
         <v>44</v>
       </c>
+      <c r="G50" s="3">
+        <v>37</v>
+      </c>
       <c r="H50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="I50" t="s">
+        <v>23</v>
       </c>
       <c r="J50" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K50" s="2">
-        <v>0.40069444444444446</v>
+        <v>0.61111111111111105</v>
       </c>
       <c r="L50">
-        <v>232.45</v>
+        <v>1.03</v>
       </c>
       <c r="M50">
-        <v>3988</v>
+        <v>488</v>
       </c>
       <c r="Q50">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="R50">
         <v>82</v>
       </c>
+      <c r="T50" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B51" s="1">
-        <v>44375</v>
+        <v>44358</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>120</v>
@@ -3422,42 +3098,48 @@
         <v>125</v>
       </c>
       <c r="E51" s="3">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F51" s="3">
         <v>44</v>
       </c>
+      <c r="G51" s="3">
+        <v>37</v>
+      </c>
       <c r="H51" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K51" s="2">
-        <v>0.40069444444444446</v>
+        <v>0.58680555555555558</v>
       </c>
       <c r="L51">
-        <v>238.28</v>
+        <v>215.49</v>
       </c>
       <c r="M51">
-        <v>3600</v>
+        <v>7181</v>
       </c>
       <c r="Q51">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="R51">
         <v>82</v>
       </c>
+      <c r="T51" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B52" s="1">
-        <v>44375</v>
+        <v>44358</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>120</v>
@@ -3466,42 +3148,48 @@
         <v>125</v>
       </c>
       <c r="E52" s="3">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F52" s="3">
         <v>44</v>
       </c>
+      <c r="G52" s="3">
+        <v>37</v>
+      </c>
       <c r="H52" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J52" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K52" s="2">
-        <v>0.40069444444444446</v>
+        <v>0.58680555555555558</v>
       </c>
       <c r="L52">
-        <v>234.7</v>
+        <v>450.5</v>
       </c>
       <c r="M52">
-        <v>3843</v>
+        <v>7527</v>
       </c>
       <c r="Q52">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="R52">
         <v>82</v>
       </c>
+      <c r="T52" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B53" s="1">
-        <v>44375</v>
+        <v>44358</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>120</v>
@@ -3510,45 +3198,48 @@
         <v>125</v>
       </c>
       <c r="E53" s="3">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F53" s="3">
         <v>44</v>
       </c>
+      <c r="G53" s="3">
+        <v>37</v>
+      </c>
       <c r="H53" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K53" s="2">
-        <v>0.40763888888888888</v>
+        <v>0.58680555555555558</v>
       </c>
       <c r="L53">
-        <v>160.55000000000001</v>
+        <v>423.8</v>
       </c>
       <c r="M53">
-        <v>3338</v>
+        <v>7474</v>
       </c>
       <c r="Q53">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="R53">
         <v>82</v>
       </c>
       <c r="T53" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B54" s="1">
-        <v>44375</v>
+        <v>44358</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>120</v>
@@ -3557,45 +3248,48 @@
         <v>125</v>
       </c>
       <c r="E54" s="3">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F54" s="3">
         <v>44</v>
       </c>
+      <c r="G54" s="3">
+        <v>37</v>
+      </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K54" s="2">
-        <v>0.40763888888888888</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="L54">
-        <v>146.66999999999999</v>
+        <v>423.83</v>
       </c>
       <c r="M54">
-        <v>3276</v>
+        <v>6633</v>
       </c>
       <c r="Q54">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="R54">
         <v>82</v>
       </c>
       <c r="T54" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B55" s="1">
-        <v>44375</v>
+        <v>44358</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>120</v>
@@ -3604,45 +3298,48 @@
         <v>125</v>
       </c>
       <c r="E55" s="3">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F55" s="3">
         <v>44</v>
       </c>
+      <c r="G55" s="3">
+        <v>37</v>
+      </c>
       <c r="H55" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J55" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K55" s="2">
-        <v>0.40763888888888888</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="L55">
-        <v>91.92</v>
+        <v>420.35</v>
       </c>
       <c r="M55">
-        <v>2515</v>
+        <v>6631</v>
       </c>
       <c r="Q55">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="R55">
         <v>82</v>
       </c>
       <c r="T55" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B56" s="1">
-        <v>44375</v>
+        <v>44358</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>120</v>
@@ -3651,484 +3348,571 @@
         <v>125</v>
       </c>
       <c r="E56" s="3">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F56" s="3">
         <v>44</v>
       </c>
+      <c r="G56" s="3">
+        <v>37</v>
+      </c>
       <c r="H56" t="s">
-        <v>117</v>
+        <v>39</v>
+      </c>
+      <c r="I56">
+        <v>3</v>
+      </c>
+      <c r="J56" t="s">
+        <v>66</v>
       </c>
       <c r="K56" s="2">
-        <v>0.4055555555555555</v>
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="L56">
+        <v>472.23</v>
+      </c>
+      <c r="M56">
+        <v>6664</v>
+      </c>
+      <c r="Q56">
+        <v>30.01</v>
+      </c>
+      <c r="R56">
+        <v>82</v>
+      </c>
+      <c r="T56" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B57" s="1">
-        <v>44375</v>
+        <v>44361</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E57" s="3">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="F57" s="3">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="G57" s="3">
+        <v>38</v>
       </c>
       <c r="H57" t="s">
-        <v>118</v>
+        <v>68</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57" t="s">
+        <v>69</v>
       </c>
       <c r="K57" s="2">
-        <v>0.4055555555555555</v>
+        <v>0.375</v>
+      </c>
+      <c r="L57">
+        <v>107.48</v>
+      </c>
+      <c r="M57">
+        <v>4782</v>
+      </c>
+      <c r="Q57">
+        <v>30.11</v>
+      </c>
+      <c r="R57">
+        <v>29.7</v>
+      </c>
+      <c r="S57">
+        <v>81.5</v>
+      </c>
+      <c r="T57" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B58" s="1">
-        <v>44363</v>
+        <v>44361</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E58" s="3">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F58" s="3">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="G58" s="3">
+        <v>38</v>
       </c>
       <c r="H58" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="K58" s="2">
-        <v>0.4236111111111111</v>
+        <v>0.375</v>
       </c>
       <c r="L58">
-        <v>3.85</v>
+        <v>61.36</v>
       </c>
       <c r="M58">
-        <v>6398</v>
+        <v>4578</v>
       </c>
       <c r="Q58">
-        <v>30.05</v>
+        <v>30.11</v>
       </c>
       <c r="R58">
-        <v>84</v>
+        <v>29.7</v>
       </c>
       <c r="S58">
-        <v>73</v>
+        <v>81.5</v>
+      </c>
+      <c r="T58" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B59" s="1">
-        <v>44363</v>
+        <v>44361</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E59" s="3">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F59" s="3">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="G59" s="3">
+        <v>38</v>
       </c>
       <c r="H59" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="I59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J59" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="K59" s="2">
-        <v>0.4236111111111111</v>
+        <v>0.375</v>
       </c>
       <c r="L59">
-        <v>3.95</v>
+        <v>106.85</v>
       </c>
       <c r="M59">
-        <v>6890</v>
+        <v>5382</v>
       </c>
       <c r="Q59">
-        <v>30.05</v>
+        <v>30.11</v>
       </c>
       <c r="R59">
-        <v>84</v>
+        <v>29.7</v>
       </c>
       <c r="S59">
-        <v>73</v>
+        <v>81.5</v>
+      </c>
+      <c r="T59" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B60" s="1">
-        <v>44363</v>
+        <v>44361</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E60" s="3">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F60" s="3">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="G60" s="3">
+        <v>38</v>
       </c>
       <c r="H60" t="s">
-        <v>82</v>
-      </c>
-      <c r="I60">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="I60" t="s">
+        <v>23</v>
       </c>
       <c r="J60" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="K60" s="2">
-        <v>0.4236111111111111</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="L60">
-        <v>3.52</v>
+        <v>-0.89</v>
       </c>
       <c r="M60">
-        <v>6035</v>
+        <v>592</v>
       </c>
       <c r="Q60">
-        <v>30.05</v>
+        <v>30.11</v>
       </c>
       <c r="R60">
-        <v>84</v>
+        <v>29.7</v>
       </c>
       <c r="S60">
-        <v>73</v>
+        <v>81.5</v>
+      </c>
+      <c r="T60" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B61" s="1">
-        <v>44363</v>
+        <v>44361</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E61" s="3">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F61" s="3">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="G61" s="3">
+        <v>38</v>
       </c>
       <c r="H61" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="I61" t="s">
         <v>23</v>
       </c>
       <c r="J61" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="K61" s="2">
-        <v>0.43055555555555558</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="L61">
-        <v>-1.49</v>
+        <v>-1.81</v>
       </c>
       <c r="M61">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="Q61">
-        <v>30.05</v>
+        <v>30.11</v>
       </c>
       <c r="R61">
-        <v>84</v>
+        <v>29.7</v>
       </c>
       <c r="S61">
-        <v>73</v>
+        <v>81.5</v>
+      </c>
+      <c r="T61" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B62" s="1">
-        <v>44363</v>
+        <v>44361</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E62" s="3">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F62" s="3">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="G62" s="3">
+        <v>38</v>
       </c>
       <c r="H62" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="I62" t="s">
         <v>23</v>
       </c>
       <c r="J62" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="K62" s="2">
-        <v>0.43055555555555558</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="L62">
-        <v>-1.85</v>
+        <v>-0.53</v>
       </c>
       <c r="M62">
-        <v>658</v>
+        <v>574</v>
       </c>
       <c r="Q62">
-        <v>30.05</v>
+        <v>30.11</v>
       </c>
       <c r="R62">
-        <v>84</v>
+        <v>29.7</v>
       </c>
       <c r="S62">
-        <v>73</v>
+        <v>81.5</v>
+      </c>
+      <c r="T62" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B63" s="1">
         <v>44363</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E63" s="3">
-        <v>169</v>
-      </c>
-      <c r="F63" s="3">
-        <v>44</v>
-      </c>
       <c r="H63" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I63" t="s">
         <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K63" s="2">
-        <v>0.43055555555555558</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="L63">
-        <v>-1.64</v>
+        <v>-1.49</v>
       </c>
       <c r="M63">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="Q63">
         <v>30.05</v>
       </c>
       <c r="R63">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="S63">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B64" s="1">
-        <v>44377</v>
+        <v>44363</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E64" s="3">
-        <v>169</v>
-      </c>
-      <c r="F64" s="3">
-        <v>44</v>
-      </c>
       <c r="H64" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="I64">
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="K64" s="2">
-        <v>0.55555555555555558</v>
+        <v>0.47222222222222227</v>
       </c>
       <c r="L64">
-        <v>3.69</v>
+        <v>12.31</v>
       </c>
       <c r="M64">
-        <v>6040</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+        <v>6348</v>
+      </c>
+      <c r="Q64">
+        <v>30.05</v>
+      </c>
+      <c r="R64">
+        <v>86</v>
+      </c>
+      <c r="S64">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B65" s="1">
-        <v>44377</v>
+        <v>44363</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="3">
-        <v>169</v>
-      </c>
-      <c r="F65" s="3">
-        <v>44</v>
-      </c>
       <c r="H65" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="I65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="K65" s="2">
-        <v>0.55555555555555558</v>
+        <v>0.47222222222222227</v>
       </c>
       <c r="L65">
-        <v>2.1800000000000002</v>
+        <v>11.59</v>
       </c>
       <c r="M65">
-        <v>6131</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+        <v>6617</v>
+      </c>
+      <c r="Q65">
+        <v>30.05</v>
+      </c>
+      <c r="R65">
+        <v>86</v>
+      </c>
+      <c r="S65">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B66" s="1">
-        <v>44377</v>
+        <v>44363</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E66" s="3">
-        <v>169</v>
-      </c>
-      <c r="F66" s="3">
-        <v>44</v>
-      </c>
       <c r="H66" t="s">
-        <v>113</v>
-      </c>
-      <c r="I66">
-        <v>3</v>
+        <v>76</v>
+      </c>
+      <c r="I66" t="s">
+        <v>23</v>
       </c>
       <c r="J66" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="K66" s="2">
-        <v>0.55555555555555558</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="L66">
-        <v>3.44</v>
+        <v>-1.89</v>
       </c>
       <c r="M66">
-        <v>6801</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+      <c r="Q66">
+        <v>30.05</v>
+      </c>
+      <c r="R66">
+        <v>86</v>
+      </c>
+      <c r="S66">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B67" s="1">
-        <v>44377</v>
+        <v>44363</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E67" s="3">
-        <v>169</v>
-      </c>
-      <c r="F67" s="3">
-        <v>44</v>
-      </c>
       <c r="H67" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="I67" t="s">
         <v>23</v>
       </c>
       <c r="J67" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="K67" s="2">
-        <v>0.5625</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="L67">
-        <v>-1.34</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="M67">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+        <v>780</v>
+      </c>
+      <c r="Q67">
+        <v>30.05</v>
+      </c>
+      <c r="R67">
+        <v>86</v>
+      </c>
+      <c r="S67">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>78</v>
       </c>
       <c r="B68" s="1">
-        <v>44377</v>
+        <v>44363</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>120</v>
@@ -4143,30 +3927,39 @@
         <v>44</v>
       </c>
       <c r="H68" t="s">
-        <v>115</v>
-      </c>
-      <c r="I68" t="s">
-        <v>23</v>
+        <v>79</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="K68" s="2">
-        <v>0.5625</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="L68">
-        <v>-1.74</v>
+        <v>3.85</v>
       </c>
       <c r="M68">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+        <v>6398</v>
+      </c>
+      <c r="Q68">
+        <v>30.05</v>
+      </c>
+      <c r="R68">
+        <v>84</v>
+      </c>
+      <c r="S68">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>78</v>
       </c>
       <c r="B69" s="1">
-        <v>44377</v>
+        <v>44363</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>120</v>
@@ -4181,30 +3974,39 @@
         <v>44</v>
       </c>
       <c r="H69" t="s">
-        <v>116</v>
-      </c>
-      <c r="I69" t="s">
-        <v>23</v>
+        <v>81</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
       </c>
       <c r="J69" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="K69" s="2">
-        <v>0.5625</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="L69">
-        <v>-1.83</v>
+        <v>3.95</v>
       </c>
       <c r="M69">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+        <v>6890</v>
+      </c>
+      <c r="Q69">
+        <v>30.05</v>
+      </c>
+      <c r="R69">
+        <v>84</v>
+      </c>
+      <c r="S69">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1">
-        <v>44160</v>
+        <v>44363</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>120</v>
@@ -4213,39 +4015,45 @@
         <v>125</v>
       </c>
       <c r="E70" s="3">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F70" s="3">
         <v>44</v>
       </c>
-      <c r="G70" s="3">
-        <v>37</v>
-      </c>
       <c r="H70" t="s">
-        <v>27</v>
-      </c>
-      <c r="I70" t="s">
-        <v>23</v>
+        <v>82</v>
+      </c>
+      <c r="I70">
+        <v>3</v>
       </c>
       <c r="J70" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="K70" s="2">
-        <v>0.3979166666666667</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="L70">
-        <v>4.7699999999999996</v>
+        <v>3.52</v>
       </c>
       <c r="M70">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+        <v>6035</v>
+      </c>
+      <c r="Q70">
+        <v>30.05</v>
+      </c>
+      <c r="R70">
+        <v>84</v>
+      </c>
+      <c r="S70">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="B71" s="1">
-        <v>44160</v>
+        <v>44363</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>120</v>
@@ -4254,39 +4062,45 @@
         <v>125</v>
       </c>
       <c r="E71" s="3">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F71" s="3">
         <v>44</v>
       </c>
-      <c r="G71" s="3">
-        <v>37</v>
-      </c>
       <c r="H71" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="I71" t="s">
         <v>23</v>
       </c>
       <c r="J71" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="K71" s="2">
-        <v>0.3979166666666667</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="L71">
-        <v>5.0999999999999996</v>
+        <v>-1.49</v>
       </c>
       <c r="M71">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+      <c r="Q71">
+        <v>30.05</v>
+      </c>
+      <c r="R71">
+        <v>84</v>
+      </c>
+      <c r="S71">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="B72" s="1">
-        <v>44160</v>
+        <v>44363</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>120</v>
@@ -4295,39 +4109,45 @@
         <v>125</v>
       </c>
       <c r="E72" s="3">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F72" s="3">
         <v>44</v>
       </c>
-      <c r="G72" s="3">
-        <v>37</v>
-      </c>
       <c r="H72" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="I72" t="s">
         <v>23</v>
       </c>
       <c r="J72" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="K72" s="2">
-        <v>0.3979166666666667</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="L72">
-        <v>3.22</v>
+        <v>-1.85</v>
       </c>
       <c r="M72">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+        <v>658</v>
+      </c>
+      <c r="Q72">
+        <v>30.05</v>
+      </c>
+      <c r="R72">
+        <v>84</v>
+      </c>
+      <c r="S72">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="B73" s="1">
-        <v>44160</v>
+        <v>44363</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>120</v>
@@ -4336,267 +4156,327 @@
         <v>125</v>
       </c>
       <c r="E73" s="3">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F73" s="3">
         <v>44</v>
       </c>
-      <c r="G73" s="3">
-        <v>37</v>
-      </c>
       <c r="H73" t="s">
-        <v>31</v>
-      </c>
-      <c r="I73">
+        <v>85</v>
+      </c>
+      <c r="I73" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" t="s">
+        <v>80</v>
+      </c>
+      <c r="K73" s="2">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="L73">
+        <v>-1.64</v>
+      </c>
+      <c r="M73">
+        <v>571</v>
+      </c>
+      <c r="Q73">
+        <v>30.05</v>
+      </c>
+      <c r="R73">
+        <v>84</v>
+      </c>
+      <c r="S73">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74" s="1">
+        <v>44364</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E74" s="3">
+        <v>150</v>
+      </c>
+      <c r="F74" s="3">
+        <v>38</v>
+      </c>
+      <c r="H74" t="s">
+        <v>87</v>
+      </c>
+      <c r="I74">
         <v>1</v>
       </c>
-      <c r="J73" t="s">
-        <v>28</v>
-      </c>
-      <c r="K73" s="2">
-        <v>0.3979166666666667</v>
-      </c>
-      <c r="L73">
-        <v>999.53</v>
-      </c>
-      <c r="M73">
-        <v>4665</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>26</v>
-      </c>
-      <c r="B74" s="1">
-        <v>44160</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E74" s="3">
-        <v>185</v>
-      </c>
-      <c r="F74" s="3">
-        <v>44</v>
-      </c>
-      <c r="G74" s="3">
-        <v>37</v>
-      </c>
-      <c r="H74" t="s">
-        <v>32</v>
-      </c>
-      <c r="I74">
+      <c r="J74" t="s">
+        <v>88</v>
+      </c>
+      <c r="K74" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L74">
+        <v>111.27</v>
+      </c>
+      <c r="M74">
+        <v>5590</v>
+      </c>
+      <c r="Q74">
+        <v>30.02</v>
+      </c>
+      <c r="R74">
+        <v>82</v>
+      </c>
+      <c r="S74">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75" s="1">
+        <v>44364</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E75" s="3">
+        <v>150</v>
+      </c>
+      <c r="F75" s="3">
+        <v>38</v>
+      </c>
+      <c r="H75" t="s">
+        <v>89</v>
+      </c>
+      <c r="I75">
         <v>2</v>
       </c>
-      <c r="J74" t="s">
-        <v>28</v>
-      </c>
-      <c r="K74" s="2">
-        <v>0.3979166666666667</v>
-      </c>
-      <c r="L74">
-        <v>734.6</v>
-      </c>
-      <c r="M74">
-        <v>4327</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>26</v>
-      </c>
-      <c r="B75" s="1">
-        <v>44160</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E75" s="3">
-        <v>185</v>
-      </c>
-      <c r="F75" s="3">
-        <v>44</v>
-      </c>
-      <c r="G75" s="3">
-        <v>37</v>
-      </c>
-      <c r="H75" t="s">
-        <v>33</v>
-      </c>
-      <c r="I75">
+      <c r="J75" t="s">
+        <v>88</v>
+      </c>
+      <c r="K75" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L75">
+        <v>100.81</v>
+      </c>
+      <c r="M75">
+        <v>5082</v>
+      </c>
+      <c r="Q75">
+        <v>30.02</v>
+      </c>
+      <c r="R75">
+        <v>82</v>
+      </c>
+      <c r="S75">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" s="1">
+        <v>44364</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E76" s="3">
+        <v>150</v>
+      </c>
+      <c r="F76" s="3">
+        <v>38</v>
+      </c>
+      <c r="H76" t="s">
+        <v>90</v>
+      </c>
+      <c r="I76">
         <v>3</v>
       </c>
-      <c r="J75" t="s">
-        <v>28</v>
-      </c>
-      <c r="K75" s="2">
-        <v>0.3979166666666667</v>
-      </c>
-      <c r="L75">
-        <v>972.57</v>
-      </c>
-      <c r="M75">
-        <v>5621</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>26</v>
-      </c>
-      <c r="B76" s="1">
-        <v>44160</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E76" s="3">
-        <v>185</v>
-      </c>
-      <c r="F76" s="3">
-        <v>44</v>
-      </c>
-      <c r="G76" s="3">
-        <v>37</v>
-      </c>
-      <c r="H76" t="s">
-        <v>34</v>
-      </c>
-      <c r="I76">
-        <v>1</v>
-      </c>
       <c r="J76" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="K76" s="2">
-        <v>0.41736111111111113</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L76">
+        <v>102.98</v>
+      </c>
+      <c r="M76">
+        <v>4291</v>
+      </c>
+      <c r="Q76">
+        <v>30.02</v>
+      </c>
+      <c r="R76">
+        <v>82</v>
+      </c>
+      <c r="S76">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="B77" s="1">
-        <v>44160</v>
+        <v>44364</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E77" s="3">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="F77" s="3">
-        <v>44</v>
-      </c>
-      <c r="G77" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H77" t="s">
-        <v>35</v>
-      </c>
-      <c r="I77">
-        <v>2</v>
+        <v>91</v>
+      </c>
+      <c r="I77" t="s">
+        <v>23</v>
       </c>
       <c r="J77" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="K77" s="2">
-        <v>0.41736111111111113</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="L77">
+        <v>-1.65</v>
+      </c>
+      <c r="M77">
+        <v>707</v>
+      </c>
+      <c r="Q77">
+        <v>30.02</v>
+      </c>
+      <c r="R77">
+        <v>82</v>
+      </c>
+      <c r="S77">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="B78" s="1">
-        <v>44160</v>
+        <v>44364</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E78" s="3">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="F78" s="3">
-        <v>44</v>
-      </c>
-      <c r="G78" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H78" t="s">
-        <v>36</v>
-      </c>
-      <c r="I78">
-        <v>3</v>
+        <v>92</v>
+      </c>
+      <c r="I78" t="s">
+        <v>23</v>
       </c>
       <c r="J78" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="K78" s="2">
-        <v>0.41736111111111113</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="L78">
+        <v>-1.72</v>
+      </c>
+      <c r="M78">
+        <v>662</v>
+      </c>
+      <c r="Q78">
+        <v>30.02</v>
+      </c>
+      <c r="R78">
+        <v>82</v>
+      </c>
+      <c r="S78">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="B79" s="1">
-        <v>44160</v>
+        <v>44364</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E79" s="3">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="F79" s="3">
-        <v>44</v>
-      </c>
-      <c r="G79" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H79" t="s">
-        <v>37</v>
-      </c>
-      <c r="I79">
-        <v>1</v>
+        <v>93</v>
+      </c>
+      <c r="I79" t="s">
+        <v>23</v>
       </c>
       <c r="J79" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="K79" s="2">
-        <v>0.44444444444444442</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="L79">
-        <v>818.74</v>
+        <v>-1.84</v>
       </c>
       <c r="M79">
-        <v>4040</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+        <v>644</v>
+      </c>
+      <c r="Q79">
+        <v>30.02</v>
+      </c>
+      <c r="R79">
+        <v>82</v>
+      </c>
+      <c r="S79">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B80" s="1">
-        <v>44160</v>
+        <v>44375</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>120</v>
@@ -4605,39 +4485,45 @@
         <v>125</v>
       </c>
       <c r="E80" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F80" s="3">
         <v>44</v>
       </c>
-      <c r="G80" s="3">
-        <v>37</v>
-      </c>
       <c r="H80" t="s">
-        <v>38</v>
-      </c>
-      <c r="I80">
-        <v>2</v>
+        <v>94</v>
+      </c>
+      <c r="I80" t="s">
+        <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="K80" s="2">
-        <v>0.44444444444444442</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="L80">
-        <v>904.21</v>
+        <v>-2.06</v>
       </c>
       <c r="M80">
-        <v>4776</v>
+        <v>701</v>
+      </c>
+      <c r="Q80">
+        <v>30.08</v>
+      </c>
+      <c r="R80">
+        <v>82</v>
+      </c>
+      <c r="T80" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B81" s="1">
-        <v>44160</v>
+        <v>44375</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>120</v>
@@ -4646,39 +4532,45 @@
         <v>125</v>
       </c>
       <c r="E81" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F81" s="3">
         <v>44</v>
       </c>
-      <c r="G81" s="3">
-        <v>37</v>
-      </c>
       <c r="H81" t="s">
-        <v>39</v>
-      </c>
-      <c r="I81">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="I81" t="s">
+        <v>23</v>
       </c>
       <c r="J81" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="K81" s="2">
-        <v>0.44444444444444442</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="L81">
-        <v>812.07</v>
+        <v>-2.04</v>
       </c>
       <c r="M81">
-        <v>4110</v>
+        <v>657</v>
+      </c>
+      <c r="Q81">
+        <v>30.08</v>
+      </c>
+      <c r="R81">
+        <v>82</v>
+      </c>
+      <c r="T81" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B82" s="1">
-        <v>44358</v>
+        <v>44375</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>120</v>
@@ -4687,48 +4579,45 @@
         <v>125</v>
       </c>
       <c r="E82" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F82" s="3">
         <v>44</v>
       </c>
-      <c r="G82" s="3">
-        <v>37</v>
-      </c>
       <c r="H82" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="I82" t="s">
         <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="K82" s="2">
-        <v>0.61111111111111105</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="L82">
-        <v>0.09</v>
+        <v>-1.59</v>
       </c>
       <c r="M82">
-        <v>680</v>
+        <v>556</v>
       </c>
       <c r="Q82">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="R82">
         <v>82</v>
       </c>
       <c r="T82" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B83" s="1">
-        <v>44358</v>
+        <v>44375</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>120</v>
@@ -4737,48 +4626,42 @@
         <v>125</v>
       </c>
       <c r="E83" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F83" s="3">
         <v>44</v>
       </c>
-      <c r="G83" s="3">
-        <v>37</v>
-      </c>
       <c r="H83" t="s">
-        <v>29</v>
-      </c>
-      <c r="I83" t="s">
-        <v>23</v>
+        <v>99</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="K83" s="2">
-        <v>0.61111111111111105</v>
+        <v>0.40069444444444446</v>
       </c>
       <c r="L83">
-        <v>2.14</v>
+        <v>232.45</v>
       </c>
       <c r="M83">
-        <v>862</v>
+        <v>3988</v>
       </c>
       <c r="Q83">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="R83">
         <v>82</v>
       </c>
-      <c r="T83" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B84" s="1">
-        <v>44358</v>
+        <v>44375</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>120</v>
@@ -4787,48 +4670,42 @@
         <v>125</v>
       </c>
       <c r="E84" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F84" s="3">
         <v>44</v>
       </c>
-      <c r="G84" s="3">
-        <v>37</v>
-      </c>
       <c r="H84" t="s">
-        <v>30</v>
-      </c>
-      <c r="I84" t="s">
-        <v>23</v>
+        <v>100</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
       </c>
       <c r="J84" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="K84" s="2">
-        <v>0.61111111111111105</v>
+        <v>0.40069444444444446</v>
       </c>
       <c r="L84">
-        <v>1.03</v>
+        <v>238.28</v>
       </c>
       <c r="M84">
-        <v>488</v>
+        <v>3600</v>
       </c>
       <c r="Q84">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="R84">
         <v>82</v>
       </c>
-      <c r="T84" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B85" s="1">
-        <v>44358</v>
+        <v>44375</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>120</v>
@@ -4837,48 +4714,42 @@
         <v>125</v>
       </c>
       <c r="E85" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F85" s="3">
         <v>44</v>
       </c>
-      <c r="G85" s="3">
-        <v>37</v>
-      </c>
       <c r="H85" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J85" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="K85" s="2">
-        <v>0.58680555555555558</v>
+        <v>0.40069444444444446</v>
       </c>
       <c r="L85">
-        <v>215.49</v>
+        <v>234.7</v>
       </c>
       <c r="M85">
-        <v>7181</v>
+        <v>3843</v>
       </c>
       <c r="Q85">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="R85">
         <v>82</v>
       </c>
-      <c r="T85" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B86" s="1">
-        <v>44358</v>
+        <v>44375</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>120</v>
@@ -4887,48 +4758,45 @@
         <v>125</v>
       </c>
       <c r="E86" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F86" s="3">
         <v>44</v>
       </c>
-      <c r="G86" s="3">
-        <v>37</v>
-      </c>
       <c r="H86" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="K86" s="2">
-        <v>0.58680555555555558</v>
+        <v>0.40763888888888888</v>
       </c>
       <c r="L86">
-        <v>450.5</v>
+        <v>160.55000000000001</v>
       </c>
       <c r="M86">
-        <v>7527</v>
+        <v>3338</v>
       </c>
       <c r="Q86">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="R86">
         <v>82</v>
       </c>
       <c r="T86" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B87" s="1">
-        <v>44358</v>
+        <v>44375</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>120</v>
@@ -4937,48 +4805,45 @@
         <v>125</v>
       </c>
       <c r="E87" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F87" s="3">
         <v>44</v>
       </c>
-      <c r="G87" s="3">
-        <v>37</v>
-      </c>
       <c r="H87" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J87" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="K87" s="2">
-        <v>0.58680555555555558</v>
+        <v>0.40763888888888888</v>
       </c>
       <c r="L87">
-        <v>423.8</v>
+        <v>146.66999999999999</v>
       </c>
       <c r="M87">
-        <v>7474</v>
+        <v>3276</v>
       </c>
       <c r="Q87">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="R87">
         <v>82</v>
       </c>
       <c r="T87" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B88" s="1">
-        <v>44358</v>
+        <v>44375</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>120</v>
@@ -4987,48 +4852,45 @@
         <v>125</v>
       </c>
       <c r="E88" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F88" s="3">
         <v>44</v>
       </c>
-      <c r="G88" s="3">
-        <v>37</v>
-      </c>
       <c r="H88" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J88" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="K88" s="2">
-        <v>0.60416666666666663</v>
+        <v>0.40763888888888888</v>
       </c>
       <c r="L88">
-        <v>423.83</v>
+        <v>91.92</v>
       </c>
       <c r="M88">
-        <v>6633</v>
+        <v>2515</v>
       </c>
       <c r="Q88">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="R88">
         <v>82</v>
       </c>
       <c r="T88" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B89" s="1">
-        <v>44358</v>
+        <v>44375</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>120</v>
@@ -5037,48 +4899,24 @@
         <v>125</v>
       </c>
       <c r="E89" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F89" s="3">
         <v>44</v>
       </c>
-      <c r="G89" s="3">
-        <v>37</v>
-      </c>
       <c r="H89" t="s">
-        <v>38</v>
-      </c>
-      <c r="I89">
-        <v>2</v>
-      </c>
-      <c r="J89" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="K89" s="2">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="L89">
-        <v>420.35</v>
-      </c>
-      <c r="M89">
-        <v>6631</v>
-      </c>
-      <c r="Q89">
-        <v>30.01</v>
-      </c>
-      <c r="R89">
-        <v>82</v>
-      </c>
-      <c r="T89" t="s">
-        <v>67</v>
+        <v>0.4055555555555555</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B90" s="1">
-        <v>44358</v>
+        <v>44375</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>120</v>
@@ -5087,277 +4925,439 @@
         <v>125</v>
       </c>
       <c r="E90" s="3">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="F90" s="3">
         <v>44</v>
       </c>
-      <c r="G90" s="3">
-        <v>37</v>
-      </c>
       <c r="H90" t="s">
-        <v>39</v>
-      </c>
-      <c r="I90">
-        <v>3</v>
-      </c>
-      <c r="J90" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="K90" s="2">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="L90">
-        <v>472.23</v>
-      </c>
-      <c r="M90">
-        <v>6664</v>
-      </c>
-      <c r="Q90">
-        <v>30.01</v>
-      </c>
-      <c r="R90">
-        <v>82</v>
-      </c>
-      <c r="T90" t="s">
-        <v>67</v>
+        <v>0.4055555555555555</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="B91" s="1">
-        <v>44180</v>
-      </c>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>103</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91" t="s">
+        <v>104</v>
+      </c>
+      <c r="K91" s="2">
+        <v>0.61805555555555558</v>
       </c>
       <c r="L91">
-        <v>2.0299999999999998</v>
+        <v>96.34</v>
       </c>
       <c r="M91">
-        <v>899</v>
+        <v>4942</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="B92" s="1">
-        <v>44180</v>
-      </c>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="H92" t="s">
-        <v>59</v>
+        <v>105</v>
+      </c>
+      <c r="I92">
+        <v>2</v>
+      </c>
+      <c r="J92" t="s">
+        <v>104</v>
+      </c>
+      <c r="K92" s="2">
+        <v>0.61805555555555558</v>
       </c>
       <c r="L92">
-        <v>3.22</v>
+        <v>94.93</v>
       </c>
       <c r="M92">
-        <v>1033</v>
+        <v>5261</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="B93" s="1">
-        <v>44180</v>
-      </c>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="H93" t="s">
-        <v>60</v>
+        <v>106</v>
+      </c>
+      <c r="I93">
+        <v>3</v>
+      </c>
+      <c r="J93" t="s">
+        <v>104</v>
+      </c>
+      <c r="K93" s="2">
+        <v>0.61805555555555558</v>
       </c>
       <c r="L93">
-        <v>2.52</v>
+        <v>91.1</v>
       </c>
       <c r="M93">
-        <v>779</v>
+        <v>4901</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="B94" s="1">
-        <v>44180</v>
-      </c>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="H94" t="s">
-        <v>61</v>
+        <v>107</v>
+      </c>
+      <c r="I94" t="s">
+        <v>23</v>
+      </c>
+      <c r="J94" t="s">
+        <v>104</v>
+      </c>
+      <c r="K94" s="2">
+        <v>0.625</v>
       </c>
       <c r="L94">
-        <v>3.04</v>
+        <v>-1.62</v>
       </c>
       <c r="M94">
-        <v>1297</v>
+        <v>582</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="B95" s="1">
-        <v>44180</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="H95" t="s">
-        <v>62</v>
+        <v>108</v>
+      </c>
+      <c r="I95" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" t="s">
+        <v>104</v>
+      </c>
+      <c r="K95" s="2">
+        <v>0.625</v>
       </c>
       <c r="L95">
-        <v>2.44</v>
+        <v>-2.0299999999999998</v>
       </c>
       <c r="M95">
-        <v>923</v>
+        <v>495</v>
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="B96" s="1">
-        <v>44180</v>
-      </c>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="H96" t="s">
-        <v>63</v>
+        <v>109</v>
+      </c>
+      <c r="I96" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" t="s">
+        <v>104</v>
+      </c>
+      <c r="K96" s="2">
+        <v>0.625</v>
       </c>
       <c r="L96">
-        <v>2.39</v>
+        <v>-1.29</v>
       </c>
       <c r="M96">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="B97" s="1">
-        <v>44180</v>
-      </c>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E97" s="3">
+        <v>169</v>
+      </c>
+      <c r="F97" s="3">
+        <v>44</v>
+      </c>
       <c r="H97" t="s">
-        <v>64</v>
+        <v>110</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97" t="s">
+        <v>111</v>
+      </c>
+      <c r="K97" s="2">
+        <v>0.55555555555555558</v>
       </c>
       <c r="L97">
-        <v>2.97</v>
+        <v>3.69</v>
       </c>
       <c r="M97">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+        <v>6040</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="B98" s="1">
-        <v>44349</v>
-      </c>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E98" s="3">
+        <v>169</v>
+      </c>
+      <c r="F98" s="3">
+        <v>44</v>
+      </c>
       <c r="H98" t="s">
-        <v>58</v>
+        <v>112</v>
+      </c>
+      <c r="I98">
+        <v>2</v>
+      </c>
+      <c r="J98" t="s">
+        <v>111</v>
+      </c>
+      <c r="K98" s="2">
+        <v>0.55555555555555558</v>
       </c>
       <c r="L98">
-        <v>1.1200000000000001</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="M98">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+        <v>6131</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="B99" s="1">
-        <v>44349</v>
-      </c>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E99" s="3">
+        <v>169</v>
+      </c>
+      <c r="F99" s="3">
+        <v>44</v>
+      </c>
       <c r="H99" t="s">
-        <v>59</v>
+        <v>113</v>
+      </c>
+      <c r="I99">
+        <v>3</v>
+      </c>
+      <c r="J99" t="s">
+        <v>111</v>
+      </c>
+      <c r="K99" s="2">
+        <v>0.55555555555555558</v>
       </c>
       <c r="L99">
-        <v>-2.38</v>
+        <v>3.44</v>
       </c>
       <c r="M99">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+        <v>6801</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="B100" s="1">
-        <v>44349</v>
-      </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E100" s="3">
+        <v>169</v>
+      </c>
+      <c r="F100" s="3">
+        <v>44</v>
+      </c>
       <c r="H100" t="s">
-        <v>60</v>
+        <v>114</v>
+      </c>
+      <c r="I100" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" t="s">
+        <v>111</v>
+      </c>
+      <c r="K100" s="2">
+        <v>0.5625</v>
       </c>
       <c r="L100">
-        <v>-1.98</v>
+        <v>-1.34</v>
       </c>
       <c r="M100">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="B101" s="1">
-        <v>44349</v>
-      </c>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E101" s="3">
+        <v>169</v>
+      </c>
+      <c r="F101" s="3">
+        <v>44</v>
+      </c>
       <c r="H101" t="s">
-        <v>62</v>
+        <v>115</v>
+      </c>
+      <c r="I101" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" t="s">
+        <v>111</v>
+      </c>
+      <c r="K101" s="2">
+        <v>0.5625</v>
       </c>
       <c r="L101">
-        <v>-1.3</v>
+        <v>-1.74</v>
       </c>
       <c r="M101">
-        <v>593</v>
-      </c>
-      <c r="T101" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="B102" s="1">
-        <v>44349</v>
-      </c>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
+        <v>44377</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E102" s="3">
+        <v>169</v>
+      </c>
+      <c r="F102" s="3">
+        <v>44</v>
+      </c>
       <c r="H102" t="s">
-        <v>63</v>
+        <v>116</v>
+      </c>
+      <c r="I102" t="s">
+        <v>23</v>
+      </c>
+      <c r="J102" t="s">
+        <v>111</v>
+      </c>
+      <c r="K102" s="2">
+        <v>0.5625</v>
       </c>
       <c r="L102">
-        <v>-1.9</v>
+        <v>-1.83</v>
       </c>
       <c r="M102">
-        <v>671</v>
-      </c>
-      <c r="T102" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>766.00614613519997</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>26</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>569.97076133120004</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>26</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>1190.4410344999999</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>26</v>
       </c>
@@ -5425,7 +5425,7 @@
         <v>13569.99913762388</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>26</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>13108.899076545171</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>26</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>10515.354415188</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>71</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>779.91680299279994</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>71</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>850.68893218879998</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>71</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>803.44092006979997</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>71</v>
       </c>
@@ -5562,8 +5562,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A103:T114">
-    <sortCondition ref="K103:K114"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T114">
+    <sortCondition ref="B2:B114"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
